--- a/documents/tests/checkList_anbara_test.xlsx
+++ b/documents/tests/checkList_anbara_test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hamid\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon6\www\anbara\documents\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B52633E-90A5-4D48-B552-5DC0135C531F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93576D6-7DC9-4C7C-8CE6-30067CEE49E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7EFB61C1-2B40-49A4-B058-302E36BE4D17}"/>
+    <workbookView xWindow="5760" yWindow="2244" windowWidth="17280" windowHeight="8880" xr2:uid="{7EFB61C1-2B40-49A4-B058-302E36BE4D17}"/>
   </bookViews>
   <sheets>
     <sheet name="فاز اول" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="249">
   <si>
     <t>چک لیست</t>
   </si>
@@ -783,6 +783,9 @@
   </si>
   <si>
     <t>PlanService همچنان getCurrentUsageDetails را برای محدودیت‌های عددی جدید (products, users, warehouses, employees, organizations) به‌درستی محاسبه می‌کند (صفحهٔ لایسنس).</t>
+  </si>
+  <si>
+    <t>بررسی اینکه از طریق url مستقیم به محتوا دسترسی داریم یا خیر به عبارتی بررسی سطوح دسترسی ها در کنترلر</t>
   </si>
 </sst>
 </file>
@@ -3049,7 +3052,9 @@
       <c r="C260" s="3"/>
     </row>
     <row r="261" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="7"/>
+      <c r="A261" s="9" t="s">
+        <v>248</v>
+      </c>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
     </row>

--- a/documents/tests/checkList_anbara_test.xlsx
+++ b/documents/tests/checkList_anbara_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon6\www\anbara\documents\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93576D6-7DC9-4C7C-8CE6-30067CEE49E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D661A4-9822-4F5D-B33B-AC57B33D327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5760" yWindow="2244" windowWidth="17280" windowHeight="8880" xr2:uid="{7EFB61C1-2B40-49A4-B058-302E36BE4D17}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="250">
   <si>
     <t>چک لیست</t>
   </si>
@@ -786,6 +786,9 @@
   </si>
   <si>
     <t>بررسی اینکه از طریق url مستقیم به محتوا دسترسی داریم یا خیر به عبارتی بررسی سطوح دسترسی ها در کنترلر</t>
+  </si>
+  <si>
+    <t>نوشتن عنوان هر صفحه در صفحات بالای صفحه</t>
   </si>
 </sst>
 </file>
@@ -3059,7 +3062,9 @@
       <c r="C261" s="3"/>
     </row>
     <row r="262" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="7"/>
+      <c r="A262" s="9" t="s">
+        <v>249</v>
+      </c>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
     </row>

--- a/documents/tests/checkList_anbara_test.xlsx
+++ b/documents/tests/checkList_anbara_test.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon6\www\anbara\documents\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D661A4-9822-4F5D-B33B-AC57B33D327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270E6DA7-3F03-4022-A466-82285D8AA90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="2244" windowWidth="17280" windowHeight="8880" xr2:uid="{7EFB61C1-2B40-49A4-B058-302E36BE4D17}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7EFB61C1-2B40-49A4-B058-302E36BE4D17}"/>
   </bookViews>
   <sheets>
     <sheet name="فاز اول" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'فاز اول'!$A$1:$C$259</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="254">
   <si>
     <t>چک لیست</t>
   </si>
@@ -789,6 +792,18 @@
   </si>
   <si>
     <t>نوشتن عنوان هر صفحه در صفحات بالای صفحه</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>باید تمام داده ها بررسی شود</t>
+  </si>
+  <si>
+    <t>ترجمه عنوان ها - دوبار نمایش ورود کاربر</t>
+  </si>
+  <si>
+    <t>خطا در برقراری با سرور</t>
   </si>
 </sst>
 </file>
@@ -1224,6 +1239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949B1AD1-E55D-40DE-8F62-86061B8921A4}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C272"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1250,46 +1266,58 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1297,34 +1325,44 @@
         <v>8</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="10" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="C10" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1334,74 +1372,94 @@
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C19" s="3"/>
     </row>
-    <row r="20" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C20" s="3"/>
     </row>
-    <row r="21" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C21" s="3"/>
     </row>
-    <row r="22" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C22" s="3"/>
     </row>
-    <row r="23" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C23" s="3"/>
     </row>
-    <row r="24" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1418,11 +1476,13 @@
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
     </row>
-    <row r="27" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1432,25 +1492,31 @@
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
     </row>
-    <row r="29" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C29" s="3"/>
     </row>
-    <row r="30" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1467,11 +1533,13 @@
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="3"/>
+      <c r="B34" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1486,20 +1554,26 @@
         <v>35</v>
       </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="C36" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="3"/>
+      <c r="B37" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C38" s="3"/>
     </row>
     <row r="39" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1544,11 +1618,13 @@
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
     </row>
-    <row r="45" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="3"/>
+      <c r="B45" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1572,18 +1648,22 @@
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B49" s="3"/>
+      <c r="B49" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C49" s="3"/>
     </row>
-    <row r="50" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A50" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="3"/>
+      <c r="B50" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1605,7 +1685,9 @@
         <v>53</v>
       </c>
       <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
+      <c r="C53" s="3" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="54" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A54" s="6" t="s">
@@ -1614,53 +1696,67 @@
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
     </row>
-    <row r="55" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A55" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="3"/>
+      <c r="B55" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C55" s="3"/>
     </row>
-    <row r="56" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A56" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="3"/>
+      <c r="B56" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A57" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="3"/>
+      <c r="B57" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C57" s="3"/>
     </row>
-    <row r="58" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A58" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="3"/>
+      <c r="B58" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A59" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="3"/>
+      <c r="B59" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A60" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="3"/>
+      <c r="B60" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A61" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="3"/>
+      <c r="B61" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C61" s="3"/>
     </row>
     <row r="62" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1698,18 +1794,22 @@
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
     </row>
-    <row r="67" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A67" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="3"/>
+      <c r="B67" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C67" s="3"/>
     </row>
-    <row r="68" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A68" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="3"/>
+      <c r="B68" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C68" s="3"/>
     </row>
     <row r="69" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1719,39 +1819,49 @@
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
     </row>
-    <row r="70" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="3"/>
+      <c r="B70" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C70" s="3"/>
     </row>
-    <row r="71" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="3"/>
+      <c r="B71" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C71" s="3"/>
     </row>
-    <row r="72" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A72" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="3"/>
+      <c r="B72" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C72" s="3"/>
     </row>
-    <row r="73" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A73" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B73" s="3"/>
+      <c r="B73" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C73" s="3"/>
     </row>
-    <row r="74" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A74" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B74" s="3"/>
+      <c r="B74" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C74" s="3"/>
     </row>
     <row r="75" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1761,60 +1871,76 @@
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
     </row>
-    <row r="76" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A76" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="3"/>
+      <c r="B76" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C76" s="3"/>
     </row>
-    <row r="77" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A77" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="3"/>
+      <c r="B77" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C77" s="3"/>
     </row>
-    <row r="78" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A78" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B78" s="3"/>
+      <c r="B78" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C78" s="3"/>
     </row>
-    <row r="79" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A79" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="3"/>
+      <c r="B79" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C79" s="3"/>
     </row>
-    <row r="80" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A80" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B80" s="3"/>
+      <c r="B80" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C80" s="3"/>
     </row>
-    <row r="81" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A81" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B81" s="3"/>
+      <c r="B81" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C81" s="3"/>
     </row>
-    <row r="82" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A82" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="3"/>
+      <c r="B82" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C82" s="3"/>
     </row>
-    <row r="83" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A83" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="3"/>
+      <c r="B83" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -3119,6 +3245,11 @@
       <c r="C272" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C259" xr:uid="{949B1AD1-E55D-40DE-8F62-86061B8921A4}">
+    <filterColumn colId="1">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/documents/tests/checkList_anbara_test.xlsx
+++ b/documents/tests/checkList_anbara_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon6\www\anbara\documents\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270E6DA7-3F03-4022-A466-82285D8AA90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729B6ACB-CAAA-458E-9E7B-6553DCE21393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7EFB61C1-2B40-49A4-B058-302E36BE4D17}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="فاز اول" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'فاز اول'!$A$1:$C$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'فاز اول'!$A$1:$C$253</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="249">
   <si>
     <t>چک لیست</t>
   </si>
@@ -294,21 +294,6 @@
   </si>
   <si>
     <t>حذف واحد با SweetAlert تأیید و موفقیت‌آمیز است</t>
-  </si>
-  <si>
-    <t>۸.۲ برندها (Brands)</t>
-  </si>
-  <si>
-    <t>لیست برندها با جستجوی زنده و فیلتر وضعیت نمایش داده می‌شود</t>
-  </si>
-  <si>
-    <t>ایجاد برند جدید با مودال (عنوان، توضیحات، فعال) کار می‌کند</t>
-  </si>
-  <si>
-    <t>ویرایش برند از طریق دکمه ویرایش کار می‌کند</t>
-  </si>
-  <si>
-    <t>حذف برند موفقیت‌آمیز است</t>
   </si>
   <si>
     <t>۸.۳ دسته‌بندی‌ها (Categories)</t>
@@ -1240,7 +1225,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949B1AD1-E55D-40DE-8F62-86061B8921A4}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C272"/>
+  <dimension ref="A1:C266"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="79.5546875" style="8" customWidth="1"/>
@@ -1256,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="23.4" x14ac:dyDescent="0.3">
@@ -1271,7 +1256,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -1280,7 +1265,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -1289,7 +1274,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -1298,7 +1283,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C6" s="3"/>
     </row>
@@ -1307,7 +1292,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -1316,7 +1301,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -1326,7 +1311,7 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1335,7 +1320,7 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
@@ -1343,7 +1328,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -1352,7 +1337,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -1361,7 +1346,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -1377,7 +1362,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C15" s="3"/>
     </row>
@@ -1386,7 +1371,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C16" s="3"/>
     </row>
@@ -1395,7 +1380,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C17" s="3"/>
     </row>
@@ -1404,7 +1389,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C18" s="3"/>
     </row>
@@ -1413,7 +1398,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C19" s="3"/>
     </row>
@@ -1422,7 +1407,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C20" s="3"/>
     </row>
@@ -1431,7 +1416,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C21" s="3"/>
     </row>
@@ -1440,7 +1425,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C22" s="3"/>
     </row>
@@ -1449,7 +1434,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C23" s="3"/>
     </row>
@@ -1458,7 +1443,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C24" s="3"/>
     </row>
@@ -1481,7 +1466,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C27" s="3"/>
     </row>
@@ -1497,7 +1482,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C29" s="3"/>
     </row>
@@ -1506,7 +1491,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C30" s="3"/>
     </row>
@@ -1515,7 +1500,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C31" s="3"/>
     </row>
@@ -1538,7 +1523,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C34" s="3"/>
     </row>
@@ -1555,7 +1540,7 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
@@ -1563,7 +1548,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C37" s="3"/>
     </row>
@@ -1572,7 +1557,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C38" s="3"/>
     </row>
@@ -1623,7 +1608,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C45" s="3"/>
     </row>
@@ -1653,7 +1638,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C49" s="3"/>
     </row>
@@ -1662,7 +1647,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C50" s="3"/>
     </row>
@@ -1686,7 +1671,7 @@
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1701,7 +1686,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C55" s="3"/>
     </row>
@@ -1710,7 +1695,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C56" s="3"/>
     </row>
@@ -1719,7 +1704,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C57" s="3"/>
     </row>
@@ -1728,7 +1713,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3"/>
     </row>
@@ -1737,7 +1722,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C59" s="3"/>
     </row>
@@ -1746,7 +1731,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C60" s="3"/>
     </row>
@@ -1755,7 +1740,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C61" s="3"/>
     </row>
@@ -1799,7 +1784,7 @@
         <v>67</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C67" s="3"/>
     </row>
@@ -1808,7 +1793,7 @@
         <v>68</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C68" s="3"/>
     </row>
@@ -1824,7 +1809,7 @@
         <v>70</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C70" s="3"/>
     </row>
@@ -1833,7 +1818,7 @@
         <v>71</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C71" s="3"/>
     </row>
@@ -1842,7 +1827,7 @@
         <v>72</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C72" s="3"/>
     </row>
@@ -1851,7 +1836,7 @@
         <v>73</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C73" s="3"/>
     </row>
@@ -1860,7 +1845,7 @@
         <v>74</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C74" s="3"/>
     </row>
@@ -1876,7 +1861,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C76" s="3"/>
     </row>
@@ -1885,7 +1870,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C77" s="3"/>
     </row>
@@ -1894,7 +1879,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C78" s="3"/>
     </row>
@@ -1903,7 +1888,7 @@
         <v>79</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C79" s="3"/>
     </row>
@@ -1912,7 +1897,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C80" s="3"/>
     </row>
@@ -1921,7 +1906,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C81" s="3"/>
     </row>
@@ -1930,7 +1915,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C82" s="3"/>
     </row>
@@ -1939,7 +1924,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C83" s="3"/>
     </row>
@@ -1959,63 +1944,63 @@
     </row>
     <row r="86" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A86" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
     </row>
     <row r="87" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A87" s="6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
     </row>
     <row r="88" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A88" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
     </row>
     <row r="89" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A89" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
     </row>
     <row r="90" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A90" s="7" t="s">
-        <v>89</v>
+      <c r="A90" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A91" s="6" t="s">
-        <v>90</v>
+      <c r="A91" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A92" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
     </row>
     <row r="93" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A93" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
     </row>
     <row r="94" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A94" s="6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -2035,7 +2020,7 @@
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B97" s="3"/>
@@ -2049,7 +2034,7 @@
       <c r="C98" s="3"/>
     </row>
     <row r="99" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="7" t="s">
         <v>96</v>
       </c>
       <c r="B99" s="3"/>
@@ -2057,14 +2042,14 @@
     </row>
     <row r="100" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A100" s="6" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
     </row>
     <row r="101" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A101" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -2091,7 +2076,7 @@
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A105" s="7" t="s">
+      <c r="A105" s="6" t="s">
         <v>101</v>
       </c>
       <c r="B105" s="3"/>
@@ -2105,148 +2090,148 @@
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A107" s="6" t="s">
-        <v>79</v>
+      <c r="A107" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A108" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
     </row>
     <row r="109" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A109" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
     </row>
     <row r="110" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A110" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
     </row>
     <row r="111" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A111" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
     </row>
     <row r="112" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A112" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
     </row>
     <row r="113" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A113" s="7" t="s">
-        <v>108</v>
+      <c r="A113" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
     </row>
     <row r="114" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A114" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
     </row>
     <row r="115" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A115" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A116" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
     </row>
     <row r="117" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A117" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
     </row>
     <row r="118" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
     </row>
     <row r="119" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A119" s="6" t="s">
-        <v>114</v>
+      <c r="A119" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
     </row>
     <row r="120" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A120" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
     </row>
     <row r="121" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A121" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
     </row>
     <row r="122" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A122" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
     </row>
     <row r="123" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A123" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
     </row>
     <row r="124" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A124" s="6" t="s">
-        <v>119</v>
+      <c r="A124" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
     </row>
     <row r="125" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A125" s="7" t="s">
-        <v>120</v>
+      <c r="A125" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
     </row>
     <row r="126" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A126" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
     </row>
     <row r="127" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A127" s="6" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -2266,7 +2251,7 @@
       <c r="C129" s="3"/>
     </row>
     <row r="130" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A130" s="7" t="s">
+      <c r="A130" s="6" t="s">
         <v>125</v>
       </c>
       <c r="B130" s="3"/>
@@ -2288,35 +2273,35 @@
     </row>
     <row r="133" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A133" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
     </row>
     <row r="134" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A134" s="6" t="s">
-        <v>128</v>
+      <c r="A134" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
     </row>
     <row r="135" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A135" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
     </row>
     <row r="136" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A136" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
     </row>
     <row r="137" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A137" s="6" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -2336,7 +2321,7 @@
       <c r="C139" s="3"/>
     </row>
     <row r="140" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A140" s="7" t="s">
+      <c r="A140" s="6" t="s">
         <v>134</v>
       </c>
       <c r="B140" s="3"/>
@@ -2357,22 +2342,22 @@
       <c r="C142" s="3"/>
     </row>
     <row r="143" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A143" s="6" t="s">
-        <v>79</v>
+      <c r="A143" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
     </row>
     <row r="144" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A144" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
     </row>
     <row r="145" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A145" s="6" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -2399,7 +2384,7 @@
       <c r="C148" s="3"/>
     </row>
     <row r="149" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A149" s="7" t="s">
+      <c r="A149" s="6" t="s">
         <v>142</v>
       </c>
       <c r="B149" s="3"/>
@@ -2413,78 +2398,78 @@
       <c r="C150" s="3"/>
     </row>
     <row r="151" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A151" s="6" t="s">
-        <v>96</v>
+      <c r="A151" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
     </row>
     <row r="152" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A152" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
     </row>
     <row r="153" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A153" s="6" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
     </row>
     <row r="154" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A154" s="6" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
     </row>
     <row r="155" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A155" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
     </row>
     <row r="156" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A156" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
     </row>
     <row r="157" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A157" s="7" t="s">
-        <v>149</v>
+      <c r="A157" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
     </row>
     <row r="158" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A158" s="6" t="s">
-        <v>150</v>
+      <c r="A158" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
     </row>
     <row r="159" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A159" s="6" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
     </row>
     <row r="160" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A160" s="6" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
     </row>
     <row r="161" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A161" s="6" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -2504,7 +2489,7 @@
       <c r="C163" s="3"/>
     </row>
     <row r="164" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A164" s="7" t="s">
+      <c r="A164" s="6" t="s">
         <v>154</v>
       </c>
       <c r="B164" s="3"/>
@@ -2518,7 +2503,7 @@
       <c r="C165" s="3"/>
     </row>
     <row r="166" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="7" t="s">
         <v>156</v>
       </c>
       <c r="B166" s="3"/>
@@ -2526,622 +2511,620 @@
     </row>
     <row r="167" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A167" s="6" t="s">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
     </row>
     <row r="168" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A168" s="6" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
     </row>
     <row r="169" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A169" s="6" t="s">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
     </row>
     <row r="170" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A170" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
     </row>
     <row r="171" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A171" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
     </row>
     <row r="172" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A172" s="7" t="s">
-        <v>161</v>
+      <c r="A172" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
     </row>
     <row r="173" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A173" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
     </row>
     <row r="174" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A174" s="6" t="s">
-        <v>127</v>
+      <c r="A174" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
     </row>
     <row r="175" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A175" s="6" t="s">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
     </row>
     <row r="176" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A176" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
     </row>
     <row r="177" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A177" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
     </row>
     <row r="178" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A178" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
     </row>
     <row r="179" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A179" s="6" t="s">
-        <v>166</v>
+      <c r="A179" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
     </row>
     <row r="180" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A180" s="7" t="s">
-        <v>167</v>
+      <c r="A180" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
     </row>
     <row r="181" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A181" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
     </row>
     <row r="182" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A182" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
     </row>
     <row r="183" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A183" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
     </row>
     <row r="184" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A184" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
     </row>
     <row r="185" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A185" s="7" t="s">
-        <v>172</v>
+      <c r="A185" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
     </row>
     <row r="186" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A186" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
     </row>
     <row r="187" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A187" s="6" t="s">
-        <v>174</v>
+      <c r="A187" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
     </row>
     <row r="188" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A188" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
     </row>
     <row r="189" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A189" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
     </row>
     <row r="190" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A190" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
     </row>
     <row r="191" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A191" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
     </row>
     <row r="192" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A192" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
     </row>
     <row r="193" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A193" s="7" t="s">
-        <v>180</v>
+      <c r="A193" s="6" t="s">
+        <v>181</v>
       </c>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
     </row>
     <row r="194" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A194" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
     </row>
     <row r="195" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A195" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
     </row>
     <row r="196" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A196" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
     </row>
     <row r="197" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A197" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
     </row>
     <row r="198" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A198" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
     </row>
     <row r="199" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A199" s="6" t="s">
-        <v>186</v>
+      <c r="A199" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
     </row>
     <row r="200" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A200" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
     </row>
     <row r="201" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A201" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
     </row>
     <row r="202" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A202" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
     </row>
     <row r="203" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A203" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
     </row>
     <row r="204" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A204" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
     </row>
     <row r="205" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A205" s="7" t="s">
-        <v>192</v>
+      <c r="A205" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
     </row>
     <row r="206" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A206" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
     </row>
-    <row r="207" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:3" s="1" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A207" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
     </row>
-    <row r="208" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
     </row>
-    <row r="209" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
     </row>
-    <row r="210" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A210" s="6" t="s">
-        <v>197</v>
+    <row r="210" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
     </row>
-    <row r="211" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
     </row>
-    <row r="212" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
     </row>
-    <row r="213" spans="1:3" s="1" customFormat="1" ht="26.4" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
     </row>
     <row r="214" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
     </row>
     <row r="215" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
     </row>
     <row r="216" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="7" t="s">
-        <v>203</v>
+      <c r="A216" s="6" t="s">
+        <v>204</v>
       </c>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
     </row>
     <row r="217" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
     </row>
     <row r="218" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="6" t="s">
-        <v>205</v>
+      <c r="A218" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
     </row>
     <row r="219" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
     </row>
     <row r="220" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
     </row>
     <row r="221" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
     </row>
     <row r="222" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
     </row>
     <row r="223" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
     </row>
     <row r="224" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="7" t="s">
-        <v>212</v>
+      <c r="A224" s="6" t="s">
+        <v>213</v>
       </c>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
     </row>
     <row r="225" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
     </row>
     <row r="226" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
     </row>
     <row r="227" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
     </row>
     <row r="228" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
     </row>
     <row r="229" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
     </row>
     <row r="230" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
     </row>
     <row r="231" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
     </row>
     <row r="232" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
     </row>
     <row r="233" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
     </row>
     <row r="234" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
     </row>
     <row r="235" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
     </row>
     <row r="236" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="6" t="s">
-        <v>224</v>
+      <c r="A236" s="7" t="s">
+        <v>225</v>
       </c>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
     </row>
     <row r="237" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="6" t="s">
-        <v>225</v>
+      <c r="A237" s="9" t="s">
+        <v>226</v>
       </c>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
     </row>
     <row r="238" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="6" t="s">
-        <v>226</v>
+      <c r="A238" s="9" t="s">
+        <v>227</v>
       </c>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
     </row>
     <row r="239" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="6" t="s">
-        <v>227</v>
+      <c r="A239" s="9" t="s">
+        <v>228</v>
       </c>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
     </row>
     <row r="240" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="6" t="s">
-        <v>228</v>
+      <c r="A240" s="9" t="s">
+        <v>229</v>
       </c>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
     </row>
     <row r="241" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="6" t="s">
-        <v>229</v>
+      <c r="A241" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
     </row>
     <row r="242" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
     </row>
     <row r="243" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
     </row>
     <row r="244" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
     </row>
     <row r="245" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
     </row>
     <row r="246" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
     </row>
     <row r="247" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
     </row>
     <row r="248" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="7" t="s">
-        <v>236</v>
+      <c r="A248" s="9" t="s">
+        <v>237</v>
       </c>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
     </row>
     <row r="249" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="9" t="s">
-        <v>237</v>
+      <c r="A249" s="7" t="s">
+        <v>238</v>
       </c>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
     </row>
     <row r="250" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
     </row>
     <row r="251" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
     </row>
     <row r="252" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
     </row>
     <row r="253" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
     </row>
     <row r="254" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="9" t="s">
-        <v>242</v>
-      </c>
+      <c r="A254" s="7"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
     </row>
     <row r="255" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="7" t="s">
+      <c r="A255" s="9" t="s">
         <v>243</v>
       </c>
       <c r="B255" s="3"/>
@@ -3155,23 +3138,17 @@
       <c r="C256" s="3"/>
     </row>
     <row r="257" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="9" t="s">
-        <v>245</v>
-      </c>
+      <c r="A257" s="7"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
     </row>
     <row r="258" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="9" t="s">
-        <v>246</v>
-      </c>
+      <c r="A258" s="7"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
     </row>
     <row r="259" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="9" t="s">
-        <v>247</v>
-      </c>
+      <c r="A259" s="7"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
     </row>
@@ -3181,16 +3158,12 @@
       <c r="C260" s="3"/>
     </row>
     <row r="261" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="9" t="s">
-        <v>248</v>
-      </c>
+      <c r="A261" s="7"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
     </row>
     <row r="262" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="9" t="s">
-        <v>249</v>
-      </c>
+      <c r="A262" s="7"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
     </row>
@@ -3205,47 +3178,17 @@
       <c r="C264" s="3"/>
     </row>
     <row r="265" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="7"/>
+      <c r="A265" s="6"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
     </row>
     <row r="266" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="7"/>
+      <c r="A266" s="6"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
     </row>
-    <row r="267" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="7"/>
-      <c r="B267" s="3"/>
-      <c r="C267" s="3"/>
-    </row>
-    <row r="268" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="7"/>
-      <c r="B268" s="3"/>
-      <c r="C268" s="3"/>
-    </row>
-    <row r="269" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="7"/>
-      <c r="B269" s="3"/>
-      <c r="C269" s="3"/>
-    </row>
-    <row r="270" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="7"/>
-      <c r="B270" s="3"/>
-      <c r="C270" s="3"/>
-    </row>
-    <row r="271" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="6"/>
-      <c r="B271" s="3"/>
-      <c r="C271" s="3"/>
-    </row>
-    <row r="272" spans="1:3" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="6"/>
-      <c r="B272" s="3"/>
-      <c r="C272" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C259" xr:uid="{949B1AD1-E55D-40DE-8F62-86061B8921A4}">
+  <autoFilter ref="A1:C253" xr:uid="{949B1AD1-E55D-40DE-8F62-86061B8921A4}">
     <filterColumn colId="1">
       <filters blank="1"/>
     </filterColumn>

--- a/documents/tests/checkList_anbara_test.xlsx
+++ b/documents/tests/checkList_anbara_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon6\www\anbara\documents\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729B6ACB-CAAA-458E-9E7B-6553DCE21393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C2D909-E3FF-416A-889F-7529BF1DBFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7EFB61C1-2B40-49A4-B058-302E36BE4D17}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="249">
   <si>
     <t>چک لیست</t>
   </si>
@@ -1935,46 +1935,58 @@
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
     </row>
-    <row r="85" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A85" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="3"/>
+      <c r="B85" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C85" s="3"/>
     </row>
-    <row r="86" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A86" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B86" s="3"/>
+      <c r="B86" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C86" s="3"/>
     </row>
-    <row r="87" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A87" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B87" s="3"/>
+      <c r="B87" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C87" s="3"/>
     </row>
-    <row r="88" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A88" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="3"/>
+      <c r="B88" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C88" s="3"/>
     </row>
-    <row r="89" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A89" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="3"/>
+      <c r="B89" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C89" s="3"/>
     </row>
-    <row r="90" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A90" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B90" s="3"/>
+      <c r="B90" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
@@ -1984,53 +1996,67 @@
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
     </row>
-    <row r="92" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A92" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="3"/>
+      <c r="B92" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C92" s="3"/>
     </row>
-    <row r="93" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A93" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B93" s="3"/>
+      <c r="B93" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C93" s="3"/>
     </row>
-    <row r="94" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A94" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B94" s="3"/>
+      <c r="B94" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C94" s="3"/>
     </row>
-    <row r="95" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A95" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B95" s="3"/>
+      <c r="B95" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C95" s="3"/>
     </row>
-    <row r="96" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A96" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B96" s="3"/>
+      <c r="B96" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C96" s="3"/>
     </row>
-    <row r="97" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A97" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B97" s="3"/>
+      <c r="B97" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C97" s="3"/>
     </row>
-    <row r="98" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:3" s="1" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A98" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B98" s="3"/>
+      <c r="B98" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="C98" s="3"/>
     </row>
     <row r="99" spans="1:3" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.5">
